--- a/九龙-马头角-瑧博/瑧博_销控明细表.xlsx
+++ b/九龙-马头角-瑧博/瑧博_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -119,12 +119,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -256,9 +250,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -641,7 +632,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -812,34 +803,34 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>18116000</v>
+        <v>14492000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>31234</v>
+        <v>24986</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>14492800</v>
+        <v>14492000</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>24988</v>
+        <v>24986</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>150天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -8238,7 +8229,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8248,7 +8239,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8337,12 +8328,12 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1812万
-$31,234/呎
-(在售)</t>
+$1449万
+$24,986/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
